--- a/tests/fixtures/19_blood_pressure_tracker/19_blood_pressure_tracker_pattern-from-draft.xlsx
+++ b/tests/fixtures/19_blood_pressure_tracker/19_blood_pressure_tracker_pattern-from-draft.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -463,52 +463,43 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>config:</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>pattern.version</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>config:</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>read.direction</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>LR</t>
         </is>
       </c>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>lbl:</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>col_datum</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Datum</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -518,7 +509,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>col_zeit</t>
+          <t>col_datum</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -528,7 +519,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Zeit</t>
+          <t>Datum</t>
         </is>
       </c>
       <c r="E3" s="2" t="n"/>
@@ -544,7 +535,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>col_systolisch</t>
+          <t>col_zeit</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -554,7 +545,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Systolisch</t>
+          <t>Zeit</t>
         </is>
       </c>
       <c r="E4" s="2" t="n"/>
@@ -570,7 +561,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>col_diastolisch</t>
+          <t>col_systolisch</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -580,7 +571,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Diastolisch</t>
+          <t>Systolisch</t>
         </is>
       </c>
       <c r="E5" s="2" t="n"/>
@@ -596,7 +587,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>col_herzfrequenz</t>
+          <t>col_diastolisch</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -606,7 +597,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Herzfrequenz</t>
+          <t>Diastolisch</t>
         </is>
       </c>
       <c r="E6" s="2" t="n"/>
@@ -622,7 +613,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>col_kommentare</t>
+          <t>col_herzfrequenz</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -632,7 +623,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Kommentare</t>
+          <t>Herzfrequenz</t>
         </is>
       </c>
       <c r="E7" s="2" t="n"/>
@@ -641,30 +632,30 @@
       <c r="H7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>var:</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>target.systolic</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>\d+</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n"/>
-      <c r="G8" s="3" t="n"/>
-      <c r="H8" s="3" t="n"/>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>lbl:</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>col_kommentare</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Kommentare</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -674,7 +665,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>target.diastolic</t>
+          <t>target.systolic</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -700,15 +691,19 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>measurement.date</t>
+          <t>target.diastolic</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>datetime</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr"/>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>\d+</t>
+        </is>
+      </c>
       <c r="E10" s="3" t="n"/>
       <c r="F10" s="3" t="n"/>
       <c r="G10" s="3" t="n"/>
@@ -722,19 +717,15 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>measurement.time</t>
+          <t>measurement.date</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>.*</t>
-        </is>
-      </c>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr"/>
       <c r="E11" s="3" t="n"/>
       <c r="F11" s="3" t="n"/>
       <c r="G11" s="3" t="n"/>
@@ -748,17 +739,17 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>measurement.systolic</t>
+          <t>measurement.time</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>\d+</t>
+          <t>.*</t>
         </is>
       </c>
       <c r="E12" s="3" t="n"/>
@@ -774,7 +765,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>measurement.diastolic</t>
+          <t>measurement.systolic</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -800,7 +791,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>measurement.heart_rate</t>
+          <t>measurement.diastolic</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -826,17 +817,17 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>measurement.comments</t>
+          <t>measurement.heart_rate</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>.*</t>
+          <t>\d+</t>
         </is>
       </c>
       <c r="E15" s="3" t="n"/>
@@ -845,46 +836,54 @@
       <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>measurement.comments</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>.*</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n"/>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>START:</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
-      <c r="G16" s="4" t="n"/>
-      <c r="H16" s="4" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>cell:D7</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>target.systolic</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="n"/>
+      <c r="G17" s="4" t="n"/>
+      <c r="H17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>cell:E7</t>
+          <t>cell:D7</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>target.diastolic</t>
+          <t>target.systolic</t>
         </is>
       </c>
       <c r="C18" s="5" t="n"/>
@@ -895,108 +894,126 @@
       <c r="H18" s="5" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>cell:E7</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>target.diastolic</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>table:*</t>
         </is>
       </c>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="6" t="n"/>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="6" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n"/>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n"/>
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>HEADER:1</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>col_datum</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>col_zeit</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>col_systolisch</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>col_diastolisch</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>col_herzfrequenz</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>col_kommentare</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="3" t="n"/>
-      <c r="B21" s="3" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="3" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>DATA:*</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>measurement.date</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>measurement.time</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>measurement.systolic</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>measurement.diastolic</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>measurement.heart_rate</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>measurement.comments</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>END:</t>
         </is>
       </c>
-      <c r="B22" s="4" t="n"/>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="4" t="n"/>
-      <c r="G22" s="4" t="n"/>
-      <c r="H22" s="4" t="n"/>
+      <c r="B23" s="4" t="n"/>
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="4" t="n"/>
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="4" t="n"/>
+      <c r="G23" s="4" t="n"/>
+      <c r="H23" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
